--- a/templates/SRI_OS_2_ยอดตั้งต้นงบดุล.xlsx
+++ b/templates/SRI_OS_2_ยอดตั้งต้นงบดุล.xlsx
@@ -10,10 +10,10 @@
     <sheet name="อ่านก่อน" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="BS-SRI Corporation" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="BS-สุธี" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS-สุดจิตต์" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="BS-ธนากร" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="BS-ธนวินท์" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="BS-เบ็ญจพร" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="BS-ธนากร" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BS-ธนวินท์" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="BS-เบ็ญจพร" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="BS-สุดจิตต์" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="รวมทุกผู้ถือ" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="พอร์ตลงทุน (รายล็อต)" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
@@ -673,7 +673,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>6 ชีท: SRI Corporation · สุธี (ป๊า) · สุดจิตต์ (ม๊า) · ธนากร · ธนวินท์ · เบ็ญจพร</t>
+          <t>6 ชีท: SRI Corporation · สุธี · ธนากร · ธนวินท์ · เบ็ญจพร · สุดจิตต์</t>
         </is>
       </c>
     </row>
@@ -852,6 +852,847 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>ยอดตั้งต้นงบดุล — SRI Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>ณ วันที่ 30/09/2026 · ราคาทุน/ตามบัญชี · ผู้ถือนิติบุคคล: ทุกรายการต้องมีหลักฐาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>รหัส</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>ชื่อบัญชี</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>ฝั่ง</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>หมวดในงบ</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>ยอดตั้งต้น *</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>หมายเหตุ / ที่มาของตัวเลข</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="15" t="inlineStr"/>
+      <c r="B5" s="15" t="inlineStr"/>
+      <c r="C5" s="15" t="inlineStr"/>
+      <c r="D5" s="15" t="inlineStr"/>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>ใส่จำนวนบวกเสมอ · ไม่มียอดให้เว้นว่าง</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>เช่น 'ยอด statement 30/09' หรือ 'ตามสัญญาเลขที่ ...'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>เงินสดและเงินฝากธนาคาร</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์หมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="18" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>ลูกหนี้ค่าเช่า</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์หมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="18" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>1210</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>ลูกหนี้ดอกเบี้ย</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์หมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="18" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>เงินมัดจำจ่าย</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์หมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="18" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>เงินให้กู้ยืม - เงินต้น</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="18" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>เงินลงทุนขายฝาก - เงินต้น</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="18" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>เงินลงทุนจำนอง - เงินต้น</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="18" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="18" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>เงินลงทุนในหลักทรัพย์</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>เงินลงทุน</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="18" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>เงินลงทุน</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="18" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>เงินลงทุน</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>สินทรัพย์</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="18" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="18" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ธนาคาร</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="18" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมกรรมการ</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="18" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมอื่น</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="18" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="18" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>ทุนตั้งต้น</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="18" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="18" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="n"/>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>รวมสินทรัพย์</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="21">
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
+        <v/>
+      </c>
+      <c r="F28" s="19" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="n"/>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>รวมหนี้สิน</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="21">
+        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
+        <v/>
+      </c>
+      <c r="F29" s="19" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>รวมส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="21">
+        <f>SUM(E25,E26)</f>
+        <v/>
+      </c>
+      <c r="F30" s="19" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n"/>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="24">
+        <f>E28-E29-E30</f>
+        <v/>
+      </c>
+      <c r="F32" s="25" t="inlineStr">
+        <is>
+          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>บัญชี</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>ธนาคาร / ช่องทาง</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>เลขท้าย</t>
+        </is>
+      </c>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>ยอดตั้งต้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="28" t="inlineStr">
+        <is>
+          <t>SRI - SCB</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="inlineStr">
+        <is>
+          <t>ไทยพาณิชย์</t>
+        </is>
+      </c>
+      <c r="D38" s="28" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>เงินสดในมือ SRI</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="inlineStr">
+        <is>
+          <t>เงินสดในมือ</t>
+        </is>
+      </c>
+      <c r="D39" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="29" t="n"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="29" t="n"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="18" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="29" t="n"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="29" t="n"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="29" t="n"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="29" t="n"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>รวมเงินสด</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="21">
+        <f>SUM(E38:E45)</f>
+        <v/>
+      </c>
+      <c r="F46" s="30" t="inlineStr">
+        <is>
+          <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="24">
+        <f>E46-E6</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E32">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="notEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E47">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="notEqual" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -871,14 +1712,14 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>ยอดตั้งต้นงบดุล — SRI Corporation</t>
+          <t>ยอดตั้งต้นงบดุล — สุธี</t>
         </is>
       </c>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>ณ วันที่ 30/09/2026 · ราคาทุน/ตามบัญชี · ผู้ถือนิติบุคคล: ทุกรายการต้องมีหลักฐาน</t>
+          <t>ณ วันที่ 30/09/2026 · ราคาทุน/ตามบัญชี · ถือในชื่อบุคคล แต่ยังเป็นกองกลางของครอบครัว</t>
         </is>
       </c>
     </row>
@@ -1173,12 +2014,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
+          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -1197,12 +2038,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -1212,7 +2053,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -1221,22 +2062,22 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
         </is>
       </c>
       <c r="E18" s="17" t="n"/>
@@ -1245,12 +2086,12 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1269,12 +2110,12 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ธนาคาร</t>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -1284,7 +2125,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
@@ -1293,12 +2134,12 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมกรรมการ</t>
+          <t>เงินกู้ธนาคาร</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -1317,12 +2158,12 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมอื่น</t>
+          <t>เงินกู้ยืมกรรมการ</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -1341,12 +2182,12 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>เงินกู้ยืมอื่น</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -1356,7 +2197,7 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>เงินกู้</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -1365,22 +2206,22 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>ทุนตั้งต้น</t>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
         </is>
       </c>
       <c r="E24" s="17" t="n"/>
@@ -1389,12 +2230,12 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>กำไรสะสม</t>
+          <t>ทุนตั้งต้น</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
@@ -1410,32 +2251,41 @@
       <c r="E25" s="17" t="n"/>
       <c r="F25" s="18" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>รวมสินทรัพย์</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17)</f>
-        <v/>
-      </c>
-      <c r="F27" s="19" t="n"/>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="19" t="n"/>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>รวมหนี้สิน</t>
+          <t>รวมสินทรัพย์</t>
         </is>
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="19" t="n"/>
       <c r="E28" s="21">
-        <f>SUM(E18,E19,E20,E21,E22,E23)</f>
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
         <v/>
       </c>
       <c r="F28" s="19" t="n"/>
@@ -1444,104 +2294,101 @@
       <c r="A29" s="19" t="n"/>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>รวมส่วนของเจ้าของ</t>
+          <t>รวมหนี้สิน</t>
         </is>
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="19" t="n"/>
       <c r="E29" s="21">
-        <f>SUM(E24,E25)</f>
+        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
         <v/>
       </c>
       <c r="F29" s="19" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="23" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>รวมส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="21">
+        <f>SUM(E25,E26)</f>
+        <v/>
+      </c>
+      <c r="F30" s="19" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n"/>
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="24">
-        <f>E27-E28-E29</f>
-        <v/>
-      </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="24">
+        <f>E28-E29-E30</f>
+        <v/>
+      </c>
+      <c r="F32" s="25" t="inlineStr">
         <is>
           <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="26" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>บัญชี</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>ธนาคาร / ช่องทาง</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>เลขท้าย</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>ยอดตั้งต้น</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="28" t="inlineStr">
-        <is>
-          <t>SRI - SCB</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="inlineStr">
-        <is>
-          <t>ไทยพาณิชย์</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="inlineStr">
-        <is>
-          <t>4412</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="28" t="inlineStr">
         <is>
-          <t>เงินสดในมือ SRI</t>
+          <t>สุธี - TTB</t>
         </is>
       </c>
       <c r="C38" s="28" t="inlineStr">
         <is>
-          <t>เงินสดในมือ</t>
+          <t>ทหารไทยธนชาต</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="E38" s="17" t="n"/>
@@ -1621,7 +2468,7 @@
       <c r="C45" s="19" t="n"/>
       <c r="D45" s="19" t="n"/>
       <c r="E45" s="21">
-        <f>SUM(E37:E44)</f>
+        <f>SUM(E38:E44)</f>
         <v/>
       </c>
       <c r="F45" s="30" t="inlineStr">
@@ -1648,7 +2495,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E31">
+  <conditionalFormatting sqref="E32">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1668,13 +2515,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1688,7 +2535,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>ยอดตั้งต้นงบดุล — สุธี (ป๊า)</t>
+          <t>ยอดตั้งต้นงบดุล — ธนากร</t>
         </is>
       </c>
     </row>
@@ -1990,12 +2837,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
+          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -2014,12 +2861,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -2029,7 +2876,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -2038,22 +2885,22 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
         </is>
       </c>
       <c r="E18" s="17" t="n"/>
@@ -2062,12 +2909,12 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -2086,12 +2933,12 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ธนาคาร</t>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -2101,7 +2948,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
@@ -2110,12 +2957,12 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมกรรมการ</t>
+          <t>เงินกู้ธนาคาร</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -2134,12 +2981,12 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมอื่น</t>
+          <t>เงินกู้ยืมกรรมการ</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -2158,12 +3005,12 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>เงินกู้ยืมอื่น</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -2173,7 +3020,7 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>เงินกู้</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -2182,22 +3029,22 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>ทุนตั้งต้น</t>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
         </is>
       </c>
       <c r="E24" s="17" t="n"/>
@@ -2206,12 +3053,12 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>กำไรสะสม</t>
+          <t>ทุนตั้งต้น</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
@@ -2227,32 +3074,41 @@
       <c r="E25" s="17" t="n"/>
       <c r="F25" s="18" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>รวมสินทรัพย์</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17)</f>
-        <v/>
-      </c>
-      <c r="F27" s="19" t="n"/>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="19" t="n"/>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>รวมหนี้สิน</t>
+          <t>รวมสินทรัพย์</t>
         </is>
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="19" t="n"/>
       <c r="E28" s="21">
-        <f>SUM(E18,E19,E20,E21,E22,E23)</f>
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
         <v/>
       </c>
       <c r="F28" s="19" t="n"/>
@@ -2261,111 +3117,122 @@
       <c r="A29" s="19" t="n"/>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>รวมส่วนของเจ้าของ</t>
+          <t>รวมหนี้สิน</t>
         </is>
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="19" t="n"/>
       <c r="E29" s="21">
-        <f>SUM(E24,E25)</f>
+        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
         <v/>
       </c>
       <c r="F29" s="19" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="23" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>รวมส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="21">
+        <f>SUM(E25,E26)</f>
+        <v/>
+      </c>
+      <c r="F30" s="19" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n"/>
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="24">
-        <f>E27-E28-E29</f>
-        <v/>
-      </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="24">
+        <f>E28-E29-E30</f>
+        <v/>
+      </c>
+      <c r="F32" s="25" t="inlineStr">
         <is>
           <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="26" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>บัญชี</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>ธนาคาร / ช่องทาง</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>เลขท้าย</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>ยอดตั้งต้น</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="28" t="inlineStr">
-        <is>
-          <t>สุธี - TTB</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="inlineStr">
-        <is>
-          <t>ทหารไทยธนชาต</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="n"/>
-    </row>
     <row r="38">
-      <c r="B38" s="18" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="29" t="n"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
+      <c r="B38" s="28" t="inlineStr">
+        <is>
+          <t>ธนากร - BBL 888</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="inlineStr">
+        <is>
+          <t>กรุงเทพ</t>
+        </is>
+      </c>
+      <c r="D38" s="28" t="inlineStr">
+        <is>
+          <t>8888</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="18" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>ธนากร - SCB</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="inlineStr">
+        <is>
+          <t>ไทยพาณิชย์</t>
+        </is>
+      </c>
+      <c r="D39" s="28" t="inlineStr">
+        <is>
+          <t>3021</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="18" t="n"/>
@@ -2412,33 +3279,55 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>รวมเงินสด</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="19" t="n"/>
-      <c r="E44" s="21">
-        <f>SUM(E37:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="30" t="inlineStr">
-        <is>
-          <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="29" t="n"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
-        </is>
-      </c>
+      <c r="B45" s="18" t="n"/>
       <c r="C45" s="22" t="n"/>
       <c r="D45" s="22" t="n"/>
-      <c r="E45" s="24">
-        <f>E44-E6</f>
+      <c r="E45" s="29" t="n"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>รวมเงินสด</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="21">
+        <f>SUM(E38:E45)</f>
+        <v/>
+      </c>
+      <c r="F46" s="30" t="inlineStr">
+        <is>
+          <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="24">
+        <f>E46-E6</f>
         <v/>
       </c>
     </row>
@@ -2447,7 +3336,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E31">
+  <conditionalFormatting sqref="E32">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2455,806 +3344,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E45">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="notEqual" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>ยอดตั้งต้นงบดุล — สุดจิตต์ (ม๊า)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>ณ วันที่ 30/09/2026 · ราคาทุน/ตามบัญชี · ถือในชื่อบุคคล แต่ยังเป็นกองกลางของครอบครัว</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>รหัส</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>ชื่อบัญชี</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>ฝั่ง</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>หมวดในงบ</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>ยอดตั้งต้น *</t>
-        </is>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>หมายเหตุ / ที่มาของตัวเลข</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="15" t="inlineStr"/>
-      <c r="B5" s="15" t="inlineStr"/>
-      <c r="C5" s="15" t="inlineStr"/>
-      <c r="D5" s="15" t="inlineStr"/>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>ใส่จำนวนบวกเสมอ · ไม่มียอดให้เว้นว่าง</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>เช่น 'ยอด statement 30/09' หรือ 'ตามสัญญาเลขที่ ...'</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>เงินสดและเงินฝากธนาคาร</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์หมุนเวียน</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="18" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>ลูกหนี้ค่าเช่า</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์หมุนเวียน</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="18" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>1210</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>ลูกหนี้ดอกเบี้ย</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์หมุนเวียน</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="18" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>เงินมัดจำจ่าย</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์หมุนเวียน</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="18" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>เงินให้กู้ยืม - เงินต้น</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="18" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>เงินลงทุนขายฝาก - เงินต้น</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="18" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>เงินลงทุนจำนอง - เงินต้น</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="18" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="n"/>
-      <c r="F13" s="18" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>1510</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="18" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>เงินลงทุนในหลักทรัพย์</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>เงินลงทุน</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="18" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>เงินลงทุน</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="18" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>สินทรัพย์</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="18" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>หนี้สิน</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>หนี้สินหมุนเวียน</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="18" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>2200</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>หนี้สิน</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>หนี้สินหมุนเวียน</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="18" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>2410</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>เงินกู้ธนาคาร</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>หนี้สิน</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>เงินกู้</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="n"/>
-      <c r="F20" s="18" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>เงินกู้ยืมกรรมการ</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>หนี้สิน</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>เงินกู้</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="18" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>เงินกู้ยืมอื่น</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>หนี้สิน</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>เงินกู้</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="18" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>2310</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>หนี้สิน</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="18" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>ทุนตั้งต้น</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>ส่วนของเจ้าของ</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>ส่วนของเจ้าของ</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="18" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>3300</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>กำไรสะสม</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>ส่วนของเจ้าของ</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>ส่วนของเจ้าของ</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="18" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>รวมสินทรัพย์</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17)</f>
-        <v/>
-      </c>
-      <c r="F27" s="19" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="n"/>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>รวมหนี้สิน</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="21">
-        <f>SUM(E18,E19,E20,E21,E22,E23)</f>
-        <v/>
-      </c>
-      <c r="F28" s="19" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>รวมส่วนของเจ้าของ</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="21">
-        <f>SUM(E24,E25)</f>
-        <v/>
-      </c>
-      <c r="F29" s="19" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="23" t="inlineStr">
-        <is>
-          <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="24">
-        <f>E27-E28-E29</f>
-        <v/>
-      </c>
-      <c r="F31" s="25" t="inlineStr">
-        <is>
-          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="26" t="inlineStr">
-        <is>
-          <t>บัญชี</t>
-        </is>
-      </c>
-      <c r="C36" s="26" t="inlineStr">
-        <is>
-          <t>ธนาคาร / ช่องทาง</t>
-        </is>
-      </c>
-      <c r="D36" s="26" t="inlineStr">
-        <is>
-          <t>เลขท้าย</t>
-        </is>
-      </c>
-      <c r="E36" s="27" t="inlineStr">
-        <is>
-          <t>ยอดตั้งต้น</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="28" t="inlineStr">
-        <is>
-          <t>สุดจิตต์ - BAY</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="inlineStr">
-        <is>
-          <t>กรุงศรีอยุธยา</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="inlineStr">
-        <is>
-          <t>7702</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="18" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="29" t="n"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="18" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="29" t="n"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="18" t="n"/>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="22" t="n"/>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>รวมเงินสด</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="19" t="n"/>
-      <c r="E44" s="21">
-        <f>SUM(E37:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="30" t="inlineStr">
-        <is>
-          <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
-        </is>
-      </c>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="24">
-        <f>E44-E6</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E31">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="notEqual" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E45">
+  <conditionalFormatting sqref="E47">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -3272,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3286,7 +3376,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>ยอดตั้งต้นงบดุล — ธนากร</t>
+          <t>ยอดตั้งต้นงบดุล — ธนวินท์</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3678,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
+          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -3612,12 +3702,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -3627,7 +3717,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -3636,22 +3726,22 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
         </is>
       </c>
       <c r="E18" s="17" t="n"/>
@@ -3660,12 +3750,12 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -3684,12 +3774,12 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ธนาคาร</t>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -3699,7 +3789,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
@@ -3708,12 +3798,12 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมกรรมการ</t>
+          <t>เงินกู้ธนาคาร</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -3732,12 +3822,12 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมอื่น</t>
+          <t>เงินกู้ยืมกรรมการ</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -3756,12 +3846,12 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>เงินกู้ยืมอื่น</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -3771,7 +3861,7 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>เงินกู้</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -3780,22 +3870,22 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>ทุนตั้งต้น</t>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
         </is>
       </c>
       <c r="E24" s="17" t="n"/>
@@ -3804,12 +3894,12 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>กำไรสะสม</t>
+          <t>ทุนตั้งต้น</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
@@ -3825,32 +3915,41 @@
       <c r="E25" s="17" t="n"/>
       <c r="F25" s="18" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>รวมสินทรัพย์</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17)</f>
-        <v/>
-      </c>
-      <c r="F27" s="19" t="n"/>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="19" t="n"/>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>รวมหนี้สิน</t>
+          <t>รวมสินทรัพย์</t>
         </is>
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="19" t="n"/>
       <c r="E28" s="21">
-        <f>SUM(E18,E19,E20,E21,E22,E23)</f>
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
         <v/>
       </c>
       <c r="F28" s="19" t="n"/>
@@ -3859,118 +3958,122 @@
       <c r="A29" s="19" t="n"/>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>รวมส่วนของเจ้าของ</t>
+          <t>รวมหนี้สิน</t>
         </is>
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="19" t="n"/>
       <c r="E29" s="21">
-        <f>SUM(E24,E25)</f>
+        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
         <v/>
       </c>
       <c r="F29" s="19" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="23" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>รวมส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="21">
+        <f>SUM(E25,E26)</f>
+        <v/>
+      </c>
+      <c r="F30" s="19" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n"/>
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="24">
-        <f>E27-E28-E29</f>
-        <v/>
-      </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="24">
+        <f>E28-E29-E30</f>
+        <v/>
+      </c>
+      <c r="F32" s="25" t="inlineStr">
         <is>
           <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="26" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>บัญชี</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>ธนาคาร / ช่องทาง</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>เลขท้าย</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>ยอดตั้งต้น</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="28" t="inlineStr">
-        <is>
-          <t>ธนากร - BBL 888</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="inlineStr">
-        <is>
-          <t>กรุงเทพ</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="inlineStr">
-        <is>
-          <t>8888</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="28" t="inlineStr">
         <is>
-          <t>ธนากร - SCB</t>
+          <t>ธนวินท์ - KBANK</t>
         </is>
       </c>
       <c r="C38" s="28" t="inlineStr">
         <is>
-          <t>ไทยพาณิชย์</t>
+          <t>กสิกรไทย</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="E38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="18" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>ธนวินท์ - BBL</t>
+        </is>
+      </c>
+      <c r="C39" s="28" t="inlineStr">
+        <is>
+          <t>กรุงเทพ</t>
+        </is>
+      </c>
+      <c r="D39" s="28" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="18" t="n"/>
@@ -4028,33 +4131,44 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="29" t="n"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>รวมเงินสด</t>
         </is>
       </c>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="21">
-        <f>SUM(E37:E44)</f>
-        <v/>
-      </c>
-      <c r="F45" s="30" t="inlineStr">
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="21">
+        <f>SUM(E38:E45)</f>
+        <v/>
+      </c>
+      <c r="F46" s="30" t="inlineStr">
         <is>
           <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="23" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
         </is>
       </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="24">
-        <f>E45-E6</f>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="24">
+        <f>E46-E6</f>
         <v/>
       </c>
     </row>
@@ -4063,7 +4177,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E31">
+  <conditionalFormatting sqref="E32">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -4071,7 +4185,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46">
+  <conditionalFormatting sqref="E47">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -4103,7 +4217,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>ยอดตั้งต้นงบดุล — ธนวินท์</t>
+          <t>ยอดตั้งต้นงบดุล — เบ็ญจพร</t>
         </is>
       </c>
     </row>
@@ -4405,12 +4519,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
+          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -4429,12 +4543,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -4444,7 +4558,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -4453,22 +4567,22 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
         </is>
       </c>
       <c r="E18" s="17" t="n"/>
@@ -4477,12 +4591,12 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -4501,12 +4615,12 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ธนาคาร</t>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -4516,7 +4630,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
@@ -4525,12 +4639,12 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมกรรมการ</t>
+          <t>เงินกู้ธนาคาร</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -4549,12 +4663,12 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมอื่น</t>
+          <t>เงินกู้ยืมกรรมการ</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -4573,12 +4687,12 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>เงินกู้ยืมอื่น</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -4588,7 +4702,7 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>เงินกู้</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -4597,22 +4711,22 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>ทุนตั้งต้น</t>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
         </is>
       </c>
       <c r="E24" s="17" t="n"/>
@@ -4621,12 +4735,12 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>กำไรสะสม</t>
+          <t>ทุนตั้งต้น</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
@@ -4642,32 +4756,41 @@
       <c r="E25" s="17" t="n"/>
       <c r="F25" s="18" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>รวมสินทรัพย์</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17)</f>
-        <v/>
-      </c>
-      <c r="F27" s="19" t="n"/>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="19" t="n"/>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>รวมหนี้สิน</t>
+          <t>รวมสินทรัพย์</t>
         </is>
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="19" t="n"/>
       <c r="E28" s="21">
-        <f>SUM(E18,E19,E20,E21,E22,E23)</f>
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
         <v/>
       </c>
       <c r="F28" s="19" t="n"/>
@@ -4676,94 +4799,91 @@
       <c r="A29" s="19" t="n"/>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>รวมส่วนของเจ้าของ</t>
+          <t>รวมหนี้สิน</t>
         </is>
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="19" t="n"/>
       <c r="E29" s="21">
-        <f>SUM(E24,E25)</f>
+        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
         <v/>
       </c>
       <c r="F29" s="19" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="23" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>รวมส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="21">
+        <f>SUM(E25,E26)</f>
+        <v/>
+      </c>
+      <c r="F30" s="19" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n"/>
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="24">
-        <f>E27-E28-E29</f>
-        <v/>
-      </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="24">
+        <f>E28-E29-E30</f>
+        <v/>
+      </c>
+      <c r="F32" s="25" t="inlineStr">
         <is>
           <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="26" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>บัญชี</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>ธนาคาร / ช่องทาง</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>เลขท้าย</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>ยอดตั้งต้น</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="28" t="inlineStr">
-        <is>
-          <t>ธนวินท์ - KBANK</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="inlineStr">
-        <is>
-          <t>กสิกรไทย</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="inlineStr">
-        <is>
-          <t>5520</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="28" t="inlineStr">
         <is>
-          <t>ธนวินท์ - BBL</t>
+          <t>เบ็ญจพร - BBL</t>
         </is>
       </c>
       <c r="C38" s="28" t="inlineStr">
@@ -4773,7 +4893,7 @@
       </c>
       <c r="D38" s="28" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="E38" s="17" t="n"/>
@@ -4853,7 +4973,7 @@
       <c r="C45" s="19" t="n"/>
       <c r="D45" s="19" t="n"/>
       <c r="E45" s="21">
-        <f>SUM(E37:E44)</f>
+        <f>SUM(E38:E44)</f>
         <v/>
       </c>
       <c r="F45" s="30" t="inlineStr">
@@ -4880,7 +5000,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E31">
+  <conditionalFormatting sqref="E32">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -4906,7 +5026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4920,7 +5040,7 @@
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>ยอดตั้งต้นงบดุล — เบ็ญจพร</t>
+          <t>ยอดตั้งต้นงบดุล — สุดจิตต์</t>
         </is>
       </c>
     </row>
@@ -5222,12 +5342,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
+          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -5246,12 +5366,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -5261,7 +5381,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -5270,22 +5390,22 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
         </is>
       </c>
       <c r="E18" s="17" t="n"/>
@@ -5294,12 +5414,12 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -5318,12 +5438,12 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ธนาคาร</t>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -5333,7 +5453,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
@@ -5342,12 +5462,12 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมกรรมการ</t>
+          <t>เงินกู้ธนาคาร</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -5366,12 +5486,12 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมอื่น</t>
+          <t>เงินกู้ยืมกรรมการ</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -5390,12 +5510,12 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>เงินกู้ยืมอื่น</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -5405,7 +5525,7 @@
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>เงินกู้</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -5414,22 +5534,22 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>ทุนตั้งต้น</t>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
         </is>
       </c>
       <c r="E24" s="17" t="n"/>
@@ -5438,12 +5558,12 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>กำไรสะสม</t>
+          <t>ทุนตั้งต้น</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
@@ -5459,32 +5579,41 @@
       <c r="E25" s="17" t="n"/>
       <c r="F25" s="18" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>รวมสินทรัพย์</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17)</f>
-        <v/>
-      </c>
-      <c r="F27" s="19" t="n"/>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="19" t="n"/>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>รวมหนี้สิน</t>
+          <t>รวมสินทรัพย์</t>
         </is>
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="19" t="n"/>
       <c r="E28" s="21">
-        <f>SUM(E18,E19,E20,E21,E22,E23)</f>
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
         <v/>
       </c>
       <c r="F28" s="19" t="n"/>
@@ -5493,100 +5622,104 @@
       <c r="A29" s="19" t="n"/>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>รวมส่วนของเจ้าของ</t>
+          <t>รวมหนี้สิน</t>
         </is>
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="19" t="n"/>
       <c r="E29" s="21">
-        <f>SUM(E24,E25)</f>
+        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
         <v/>
       </c>
       <c r="F29" s="19" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="22" t="n"/>
-      <c r="B31" s="23" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>รวมส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="21">
+        <f>SUM(E25,E26)</f>
+        <v/>
+      </c>
+      <c r="F30" s="19" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n"/>
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="24">
-        <f>E27-E28-E29</f>
-        <v/>
-      </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="24">
+        <f>E28-E29-E30</f>
+        <v/>
+      </c>
+      <c r="F32" s="25" t="inlineStr">
         <is>
           <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="26" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>บัญชี</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>ธนาคาร / ช่องทาง</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>เลขท้าย</t>
         </is>
       </c>
-      <c r="E36" s="27" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>ยอดตั้งต้น</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="28" t="inlineStr">
-        <is>
-          <t>เบ็ญจพร - BBL</t>
-        </is>
-      </c>
-      <c r="C37" s="28" t="inlineStr">
-        <is>
-          <t>กรุงเทพ</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="inlineStr">
-        <is>
-          <t>6045</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="n"/>
-    </row>
     <row r="38">
-      <c r="B38" s="18" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="29" t="n"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
+      <c r="B38" s="28" t="inlineStr">
+        <is>
+          <t>สุดจิตต์ - BAY</t>
+        </is>
+      </c>
+      <c r="C38" s="28" t="inlineStr">
+        <is>
+          <t>กรุงศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="D38" s="28" t="inlineStr">
+        <is>
+          <t>7702</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="18" t="n"/>
@@ -5644,33 +5777,44 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="29" t="n"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>รวมเงินสด</t>
         </is>
       </c>
-      <c r="C44" s="19" t="n"/>
-      <c r="D44" s="19" t="n"/>
-      <c r="E44" s="21">
-        <f>SUM(E37:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="30" t="inlineStr">
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="21">
+        <f>SUM(E38:E44)</f>
+        <v/>
+      </c>
+      <c r="F45" s="30" t="inlineStr">
         <is>
           <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="23" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
         </is>
       </c>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="24">
-        <f>E44-E6</f>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="24">
+        <f>E45-E6</f>
         <v/>
       </c>
     </row>
@@ -5679,7 +5823,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E31">
+  <conditionalFormatting sqref="E32">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5687,7 +5831,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E45">
+  <conditionalFormatting sqref="E46">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -5750,22 +5894,22 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
+          <t>ธนากร</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>ธนวินท์</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>เบ็ญจพร</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
           <t>สุดจิตต์</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>ธนากร</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>ธนวินท์</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>เบ็ญจพร</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -5791,27 +5935,27 @@
         </is>
       </c>
       <c r="B6" s="17">
-        <f>'BS-SRI Corporation'!E27</f>
+        <f>'BS-SRI Corporation'!E28</f>
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>'BS-สุธี'!E27</f>
+        <f>'BS-สุธี'!E28</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>'BS-สุดจิตต์'!E27</f>
+        <f>'BS-ธนากร'!E28</f>
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>'BS-ธนากร'!E27</f>
+        <f>'BS-ธนวินท์'!E28</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>'BS-ธนวินท์'!E27</f>
+        <f>'BS-เบ็ญจพร'!E28</f>
         <v/>
       </c>
       <c r="G6" s="17">
-        <f>'BS-เบ็ญจพร'!E27</f>
+        <f>'BS-สุดจิตต์'!E28</f>
         <v/>
       </c>
       <c r="H6" s="24">
@@ -5826,27 +5970,27 @@
         </is>
       </c>
       <c r="B7" s="17">
-        <f>'BS-SRI Corporation'!E28</f>
+        <f>'BS-SRI Corporation'!E29</f>
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>'BS-สุธี'!E28</f>
+        <f>'BS-สุธี'!E29</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>'BS-สุดจิตต์'!E28</f>
+        <f>'BS-ธนากร'!E29</f>
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>'BS-ธนากร'!E28</f>
+        <f>'BS-ธนวินท์'!E29</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>'BS-ธนวินท์'!E28</f>
+        <f>'BS-เบ็ญจพร'!E29</f>
         <v/>
       </c>
       <c r="G7" s="17">
-        <f>'BS-เบ็ญจพร'!E28</f>
+        <f>'BS-สุดจิตต์'!E29</f>
         <v/>
       </c>
       <c r="H7" s="24">
@@ -5861,27 +6005,27 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>'BS-SRI Corporation'!E29</f>
+        <f>'BS-SRI Corporation'!E30</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>'BS-สุธี'!E29</f>
+        <f>'BS-สุธี'!E30</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>'BS-สุดจิตต์'!E29</f>
+        <f>'BS-ธนากร'!E30</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>'BS-ธนากร'!E29</f>
+        <f>'BS-ธนวินท์'!E30</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>'BS-ธนวินท์'!E29</f>
+        <f>'BS-เบ็ญจพร'!E30</f>
         <v/>
       </c>
       <c r="G8" s="17">
-        <f>'BS-เบ็ญจพร'!E29</f>
+        <f>'BS-สุดจิตต์'!E30</f>
         <v/>
       </c>
       <c r="H8" s="24">
@@ -5896,27 +6040,27 @@
         </is>
       </c>
       <c r="B10" s="24">
-        <f>'BS-SRI Corporation'!E31</f>
+        <f>'BS-SRI Corporation'!E32</f>
         <v/>
       </c>
       <c r="C10" s="24">
-        <f>'BS-สุธี'!E31</f>
+        <f>'BS-สุธี'!E32</f>
         <v/>
       </c>
       <c r="D10" s="24">
-        <f>'BS-สุดจิตต์'!E31</f>
+        <f>'BS-ธนากร'!E32</f>
         <v/>
       </c>
       <c r="E10" s="24">
-        <f>'BS-ธนากร'!E31</f>
+        <f>'BS-ธนวินท์'!E32</f>
         <v/>
       </c>
       <c r="F10" s="24">
-        <f>'BS-ธนวินท์'!E31</f>
+        <f>'BS-เบ็ญจพร'!E32</f>
         <v/>
       </c>
       <c r="G10" s="24">
-        <f>'BS-เบ็ญจพร'!E31</f>
+        <f>'BS-สุดจิตต์'!E32</f>
         <v/>
       </c>
     </row>
@@ -5934,27 +6078,27 @@
         </is>
       </c>
       <c r="B13" s="17">
-        <f>'BS-SRI Corporation'!E17</f>
+        <f>'BS-SRI Corporation'!E18</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>'BS-สุธี'!E17</f>
+        <f>'BS-สุธี'!E18</f>
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>'BS-สุดจิตต์'!E17</f>
+        <f>'BS-ธนากร'!E18</f>
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>'BS-ธนากร'!E17</f>
+        <f>'BS-ธนวินท์'!E18</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>'BS-ธนวินท์'!E17</f>
+        <f>'BS-เบ็ญจพร'!E18</f>
         <v/>
       </c>
       <c r="G13" s="17">
-        <f>'BS-เบ็ญจพร'!E17</f>
+        <f>'BS-สุดจิตต์'!E18</f>
         <v/>
       </c>
       <c r="H13" s="24">
@@ -5969,27 +6113,27 @@
         </is>
       </c>
       <c r="B14" s="17">
-        <f>'BS-SRI Corporation'!E23</f>
+        <f>'BS-SRI Corporation'!E24</f>
         <v/>
       </c>
       <c r="C14" s="17">
-        <f>'BS-สุธี'!E23</f>
+        <f>'BS-สุธี'!E24</f>
         <v/>
       </c>
       <c r="D14" s="17">
-        <f>'BS-สุดจิตต์'!E23</f>
+        <f>'BS-ธนากร'!E24</f>
         <v/>
       </c>
       <c r="E14" s="17">
-        <f>'BS-ธนากร'!E23</f>
+        <f>'BS-ธนวินท์'!E24</f>
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>'BS-ธนวินท์'!E23</f>
+        <f>'BS-เบ็ญจพร'!E24</f>
         <v/>
       </c>
       <c r="G14" s="17">
-        <f>'BS-เบ็ญจพร'!E23</f>
+        <f>'BS-สุดจิตต์'!E24</f>
         <v/>
       </c>
       <c r="H14" s="24">
@@ -8024,7 +8168,7 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="A6:A205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
-      <formula1>"SRI Corporation,สุธี,สุดจิตต์,ธนากร,ธนวินท์,เบ็ญจพร"</formula1>
+      <formula1>"SRI Corporation,สุธี,ธนากร,ธนวินท์,เบ็ญจพร,สุดจิตต์"</formula1>
     </dataValidation>
     <dataValidation sqref="B6:B205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="เลือกจากรายการเท่านั้น" type="list">
       <formula1>"หุ้นไทย,หุ้น US,ETF,กองทุน,Crypto,ทองคำ,พันธบัตร"</formula1>

--- a/templates/SRI_OS_2_ยอดตั้งต้นงบดุล.xlsx
+++ b/templates/SRI_OS_2_ยอดตั้งต้นงบดุล.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1005,12 +1005,12 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำจ่าย</t>
+          <t>ลูกหนี้อื่น (รอรับเงิน)</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -1029,12 +1029,12 @@
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้ยืม - เงินต้น</t>
+          <t>เงินมัดจำจ่าย</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E10" s="17" t="n"/>
@@ -1053,12 +1053,12 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนขายฝาก - เงินต้น</t>
+          <t>ภาษีถูกหัก ณ ที่จ่ายรอเครดิต</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E11" s="17" t="n"/>
@@ -1077,12 +1077,12 @@
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนจำนอง - เงินต้น</t>
+          <t>สินทรัพย์หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E12" s="17" t="n"/>
@@ -1101,12 +1101,12 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้ยืม - เงินต้น</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E13" s="17" t="n"/>
@@ -1125,12 +1125,12 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
+          <t>เงินให้กู้ยืมแบบมีสินทรัพย์ค้ำประกัน - เงินต้น</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E14" s="17" t="n"/>
@@ -1149,12 +1149,12 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในหลักทรัพย์</t>
+          <t>เงินลงทุนขายฝาก - เงินต้น</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E15" s="17" t="n"/>
@@ -1173,12 +1173,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
+          <t>เงินลงทุนจำนอง - เงินต้น</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E16" s="17" t="n"/>
@@ -1197,12 +1197,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการเช่า</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -1221,12 +1221,12 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E18" s="17" t="n"/>
@@ -1245,22 +1245,22 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการขาย</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E19" s="17" t="n"/>
@@ -1269,22 +1269,22 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
+          <t>เงินลงทุนในหุ้นและหลักทรัพย์</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
@@ -1293,22 +1293,22 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ธนาคาร</t>
+          <t>เงินลงทุนในทองคำ คริปโต และสินทรัพย์ทางเลือก</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E21" s="17" t="n"/>
@@ -1317,22 +1317,22 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมกรรมการ</t>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E22" s="17" t="n"/>
@@ -1341,22 +1341,22 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมอื่น</t>
+          <t>สินทรัพย์ไม่หมุนเวียน</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>สินทรัพย์ไม่หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -1365,17 +1365,17 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -1389,22 +1389,22 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>ทุนตั้งต้น</t>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E25" s="17" t="n"/>
@@ -1413,257 +1413,497 @@
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>กำไรสะสม</t>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E26" s="17" t="n"/>
       <c r="F26" s="18" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="18" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="19" t="n"/>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ธนาคาร</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมกรรมการ</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมอื่น</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียน</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="18" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>ทุนตั้งต้น</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="18" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="18" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนเกินทุนจากการตีราคา (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="18" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>ผลต่างอัตราแลกเปลี่ยนจากการแปลงค่า (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="18" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>รวมสินทรัพย์</t>
         </is>
       </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
-        <v/>
-      </c>
-      <c r="F28" s="19" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="21">
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E23,E24)</f>
+        <v/>
+      </c>
+      <c r="F38" s="19" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>รวมหนี้สิน</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="21">
-        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
-        <v/>
-      </c>
-      <c r="F29" s="19" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="21">
+        <f>SUM(E25,E26,E27,E28,E29,E30,E31,E32)</f>
+        <v/>
+      </c>
+      <c r="F39" s="19" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>รวมส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="21">
-        <f>SUM(E25,E26)</f>
-        <v/>
-      </c>
-      <c r="F30" s="19" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="21">
+        <f>SUM(E33,E34,E35,E36)</f>
+        <v/>
+      </c>
+      <c r="F40" s="19" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n"/>
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="24">
-        <f>E28-E29-E30</f>
-        <v/>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>บัญชี</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>ธนาคาร / ช่องทาง</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="inlineStr">
-        <is>
-          <t>เลขท้าย</t>
-        </is>
-      </c>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>ยอดตั้งต้น</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="28" t="inlineStr">
-        <is>
-          <t>SRI - SCB</t>
-        </is>
-      </c>
-      <c r="C38" s="28" t="inlineStr">
-        <is>
-          <t>ไทยพาณิชย์</t>
-        </is>
-      </c>
-      <c r="D38" s="28" t="inlineStr">
-        <is>
-          <t>4412</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="28" t="inlineStr">
-        <is>
-          <t>เงินสดในมือ SRI</t>
-        </is>
-      </c>
-      <c r="C39" s="28" t="inlineStr">
-        <is>
-          <t>เงินสดในมือ</t>
-        </is>
-      </c>
-      <c r="D39" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="29" t="n"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="18" t="n"/>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="22" t="n"/>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="E42" s="24">
+        <f>E38-E39-E40</f>
+        <v/>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>บัญชี</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>ธนาคาร / ช่องทาง</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>เลขท้าย</t>
+        </is>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>ยอดตั้งต้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="28" t="inlineStr">
+        <is>
+          <t>SRI - SCB</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>ไทยพาณิชย์</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="28" t="inlineStr">
+        <is>
+          <t>เงินสดในมือ SRI</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="inlineStr">
+        <is>
+          <t>เงินสดในมือ</t>
+        </is>
+      </c>
+      <c r="D49" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="29" t="n"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="2" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="29" t="n"/>
-      <c r="F44" s="2" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="29" t="n"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="18" t="n"/>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="29" t="n"/>
-      <c r="F45" s="2" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="29" t="n"/>
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="20" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="29" t="n"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="29" t="n"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="20" t="inlineStr">
         <is>
           <t>รวมเงินสด</t>
         </is>
       </c>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="19" t="n"/>
-      <c r="E46" s="21">
-        <f>SUM(E38:E45)</f>
-        <v/>
-      </c>
-      <c r="F46" s="30" t="inlineStr">
+      <c r="C56" s="19" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="21">
+        <f>SUM(E48:E55)</f>
+        <v/>
+      </c>
+      <c r="F56" s="30" t="inlineStr">
         <is>
           <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="23" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
         </is>
       </c>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n"/>
-      <c r="E47" s="24">
-        <f>E46-E6</f>
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="22" t="n"/>
+      <c r="E57" s="24">
+        <f>E56-E6</f>
         <v/>
       </c>
     </row>
@@ -1672,7 +1912,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E32">
+  <conditionalFormatting sqref="E42">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1680,7 +1920,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E47">
+  <conditionalFormatting sqref="E57">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -1698,7 +1938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1846,12 +2086,12 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำจ่าย</t>
+          <t>ลูกหนี้อื่น (รอรับเงิน)</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -1870,12 +2110,12 @@
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้ยืม - เงินต้น</t>
+          <t>เงินมัดจำจ่าย</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -1885,7 +2125,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E10" s="17" t="n"/>
@@ -1894,12 +2134,12 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนขายฝาก - เงินต้น</t>
+          <t>ภาษีถูกหัก ณ ที่จ่ายรอเครดิต</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -1909,7 +2149,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E11" s="17" t="n"/>
@@ -1918,12 +2158,12 @@
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนจำนอง - เงินต้น</t>
+          <t>สินทรัพย์หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -1933,7 +2173,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E12" s="17" t="n"/>
@@ -1942,12 +2182,12 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้ยืม - เงินต้น</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -1957,7 +2197,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E13" s="17" t="n"/>
@@ -1966,12 +2206,12 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
+          <t>เงินให้กู้ยืมแบบมีสินทรัพย์ค้ำประกัน - เงินต้น</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -1981,7 +2221,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E14" s="17" t="n"/>
@@ -1990,12 +2230,12 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในหลักทรัพย์</t>
+          <t>เงินลงทุนขายฝาก - เงินต้น</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -2005,7 +2245,7 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E15" s="17" t="n"/>
@@ -2014,12 +2254,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
+          <t>เงินลงทุนจำนอง - เงินต้น</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -2029,7 +2269,7 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E16" s="17" t="n"/>
@@ -2038,12 +2278,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการเช่า</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -2053,7 +2293,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -2062,12 +2302,12 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -2077,7 +2317,7 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E18" s="17" t="n"/>
@@ -2086,22 +2326,22 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการขาย</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E19" s="17" t="n"/>
@@ -2110,22 +2350,22 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
+          <t>เงินลงทุนในหุ้นและหลักทรัพย์</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
@@ -2134,22 +2374,22 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ธนาคาร</t>
+          <t>เงินลงทุนในทองคำ คริปโต และสินทรัพย์ทางเลือก</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E21" s="17" t="n"/>
@@ -2158,22 +2398,22 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมกรรมการ</t>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E22" s="17" t="n"/>
@@ -2182,22 +2422,22 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมอื่น</t>
+          <t>สินทรัพย์ไม่หมุนเวียน</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>สินทรัพย์ไม่หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -2206,17 +2446,17 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -2230,22 +2470,22 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>ทุนตั้งต้น</t>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E25" s="17" t="n"/>
@@ -2254,239 +2494,479 @@
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>กำไรสะสม</t>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E26" s="17" t="n"/>
       <c r="F26" s="18" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="18" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="19" t="n"/>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ธนาคาร</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมกรรมการ</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมอื่น</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียน</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="18" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>ทุนตั้งต้น</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="18" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="18" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนเกินทุนจากการตีราคา (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="18" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>ผลต่างอัตราแลกเปลี่ยนจากการแปลงค่า (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="18" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>รวมสินทรัพย์</t>
         </is>
       </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
-        <v/>
-      </c>
-      <c r="F28" s="19" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="21">
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E23,E24)</f>
+        <v/>
+      </c>
+      <c r="F38" s="19" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>รวมหนี้สิน</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="21">
-        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
-        <v/>
-      </c>
-      <c r="F29" s="19" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="21">
+        <f>SUM(E25,E26,E27,E28,E29,E30,E31,E32)</f>
+        <v/>
+      </c>
+      <c r="F39" s="19" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>รวมส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="21">
-        <f>SUM(E25,E26)</f>
-        <v/>
-      </c>
-      <c r="F30" s="19" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="21">
+        <f>SUM(E33,E34,E35,E36)</f>
+        <v/>
+      </c>
+      <c r="F40" s="19" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n"/>
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="24">
-        <f>E28-E29-E30</f>
-        <v/>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>บัญชี</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>ธนาคาร / ช่องทาง</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="inlineStr">
-        <is>
-          <t>เลขท้าย</t>
-        </is>
-      </c>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>ยอดตั้งต้น</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="28" t="inlineStr">
-        <is>
-          <t>สุธี - TTB</t>
-        </is>
-      </c>
-      <c r="C38" s="28" t="inlineStr">
-        <is>
-          <t>ทหารไทยธนชาต</t>
-        </is>
-      </c>
-      <c r="D38" s="28" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="18" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="29" t="n"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="18" t="n"/>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="22" t="n"/>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="E42" s="24">
+        <f>E38-E39-E40</f>
+        <v/>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>บัญชี</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>ธนาคาร / ช่องทาง</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>เลขท้าย</t>
+        </is>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>ยอดตั้งต้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="28" t="inlineStr">
+        <is>
+          <t>สุธี - TTB</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>ทหารไทยธนชาต</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="22" t="n"/>
+      <c r="D49" s="22" t="n"/>
+      <c r="E49" s="29" t="n"/>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="2" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="29" t="n"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="29" t="n"/>
-      <c r="F44" s="2" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="20" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="29" t="n"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="29" t="n"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="29" t="n"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>รวมเงินสด</t>
         </is>
       </c>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="21">
-        <f>SUM(E38:E44)</f>
-        <v/>
-      </c>
-      <c r="F45" s="30" t="inlineStr">
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="21">
+        <f>SUM(E48:E54)</f>
+        <v/>
+      </c>
+      <c r="F55" s="30" t="inlineStr">
         <is>
           <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="23" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
         </is>
       </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="24">
-        <f>E45-E6</f>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="24">
+        <f>E55-E6</f>
         <v/>
       </c>
     </row>
@@ -2495,7 +2975,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E32">
+  <conditionalFormatting sqref="E42">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -2503,7 +2983,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46">
+  <conditionalFormatting sqref="E56">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -2521,7 +3001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2669,12 +3149,12 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำจ่าย</t>
+          <t>ลูกหนี้อื่น (รอรับเงิน)</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -2693,12 +3173,12 @@
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้ยืม - เงินต้น</t>
+          <t>เงินมัดจำจ่าย</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -2708,7 +3188,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E10" s="17" t="n"/>
@@ -2717,12 +3197,12 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนขายฝาก - เงินต้น</t>
+          <t>ภาษีถูกหัก ณ ที่จ่ายรอเครดิต</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -2732,7 +3212,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E11" s="17" t="n"/>
@@ -2741,12 +3221,12 @@
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนจำนอง - เงินต้น</t>
+          <t>สินทรัพย์หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -2756,7 +3236,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E12" s="17" t="n"/>
@@ -2765,12 +3245,12 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้ยืม - เงินต้น</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -2780,7 +3260,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E13" s="17" t="n"/>
@@ -2789,12 +3269,12 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
+          <t>เงินให้กู้ยืมแบบมีสินทรัพย์ค้ำประกัน - เงินต้น</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -2804,7 +3284,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E14" s="17" t="n"/>
@@ -2813,12 +3293,12 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในหลักทรัพย์</t>
+          <t>เงินลงทุนขายฝาก - เงินต้น</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -2828,7 +3308,7 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E15" s="17" t="n"/>
@@ -2837,12 +3317,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
+          <t>เงินลงทุนจำนอง - เงินต้น</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -2852,7 +3332,7 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E16" s="17" t="n"/>
@@ -2861,12 +3341,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการเช่า</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -2876,7 +3356,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -2885,12 +3365,12 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -2900,7 +3380,7 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E18" s="17" t="n"/>
@@ -2909,22 +3389,22 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการขาย</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E19" s="17" t="n"/>
@@ -2933,22 +3413,22 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
+          <t>เงินลงทุนในหุ้นและหลักทรัพย์</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
@@ -2957,22 +3437,22 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ธนาคาร</t>
+          <t>เงินลงทุนในทองคำ คริปโต และสินทรัพย์ทางเลือก</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E21" s="17" t="n"/>
@@ -2981,22 +3461,22 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมกรรมการ</t>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E22" s="17" t="n"/>
@@ -3005,22 +3485,22 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมอื่น</t>
+          <t>สินทรัพย์ไม่หมุนเวียน</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>สินทรัพย์ไม่หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -3029,17 +3509,17 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -3053,22 +3533,22 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>ทุนตั้งต้น</t>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E25" s="17" t="n"/>
@@ -3077,257 +3557,497 @@
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>กำไรสะสม</t>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E26" s="17" t="n"/>
       <c r="F26" s="18" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="18" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="19" t="n"/>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ธนาคาร</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมกรรมการ</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมอื่น</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียน</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="18" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>ทุนตั้งต้น</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="18" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="18" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนเกินทุนจากการตีราคา (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="18" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>ผลต่างอัตราแลกเปลี่ยนจากการแปลงค่า (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="18" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>รวมสินทรัพย์</t>
         </is>
       </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
-        <v/>
-      </c>
-      <c r="F28" s="19" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="21">
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E23,E24)</f>
+        <v/>
+      </c>
+      <c r="F38" s="19" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>รวมหนี้สิน</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="21">
-        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
-        <v/>
-      </c>
-      <c r="F29" s="19" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="21">
+        <f>SUM(E25,E26,E27,E28,E29,E30,E31,E32)</f>
+        <v/>
+      </c>
+      <c r="F39" s="19" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>รวมส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="21">
-        <f>SUM(E25,E26)</f>
-        <v/>
-      </c>
-      <c r="F30" s="19" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="21">
+        <f>SUM(E33,E34,E35,E36)</f>
+        <v/>
+      </c>
+      <c r="F40" s="19" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n"/>
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="24">
-        <f>E28-E29-E30</f>
-        <v/>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>บัญชี</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>ธนาคาร / ช่องทาง</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="inlineStr">
-        <is>
-          <t>เลขท้าย</t>
-        </is>
-      </c>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>ยอดตั้งต้น</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="28" t="inlineStr">
-        <is>
-          <t>ธนากร - BBL 888</t>
-        </is>
-      </c>
-      <c r="C38" s="28" t="inlineStr">
-        <is>
-          <t>กรุงเทพ</t>
-        </is>
-      </c>
-      <c r="D38" s="28" t="inlineStr">
-        <is>
-          <t>8888</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="28" t="inlineStr">
-        <is>
-          <t>ธนากร - SCB</t>
-        </is>
-      </c>
-      <c r="C39" s="28" t="inlineStr">
-        <is>
-          <t>ไทยพาณิชย์</t>
-        </is>
-      </c>
-      <c r="D39" s="28" t="inlineStr">
-        <is>
-          <t>3021</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="29" t="n"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="18" t="n"/>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="22" t="n"/>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="E42" s="24">
+        <f>E38-E39-E40</f>
+        <v/>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>บัญชี</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>ธนาคาร / ช่องทาง</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>เลขท้าย</t>
+        </is>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>ยอดตั้งต้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="28" t="inlineStr">
+        <is>
+          <t>ธนากร - BBL 888</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>กรุงเทพ</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="inlineStr">
+        <is>
+          <t>8888</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="28" t="inlineStr">
+        <is>
+          <t>ธนากร - SCB</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="inlineStr">
+        <is>
+          <t>ไทยพาณิชย์</t>
+        </is>
+      </c>
+      <c r="D49" s="28" t="inlineStr">
+        <is>
+          <t>3021</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="29" t="n"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="2" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="29" t="n"/>
-      <c r="F44" s="2" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="29" t="n"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="18" t="n"/>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="29" t="n"/>
-      <c r="F45" s="2" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="29" t="n"/>
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="20" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="29" t="n"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="29" t="n"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="20" t="inlineStr">
         <is>
           <t>รวมเงินสด</t>
         </is>
       </c>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="19" t="n"/>
-      <c r="E46" s="21">
-        <f>SUM(E38:E45)</f>
-        <v/>
-      </c>
-      <c r="F46" s="30" t="inlineStr">
+      <c r="C56" s="19" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="21">
+        <f>SUM(E48:E55)</f>
+        <v/>
+      </c>
+      <c r="F56" s="30" t="inlineStr">
         <is>
           <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="23" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
         </is>
       </c>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n"/>
-      <c r="E47" s="24">
-        <f>E46-E6</f>
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="22" t="n"/>
+      <c r="E57" s="24">
+        <f>E56-E6</f>
         <v/>
       </c>
     </row>
@@ -3336,7 +4056,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E32">
+  <conditionalFormatting sqref="E42">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3344,7 +4064,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E47">
+  <conditionalFormatting sqref="E57">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -3362,7 +4082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3510,12 +4230,12 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำจ่าย</t>
+          <t>ลูกหนี้อื่น (รอรับเงิน)</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -3534,12 +4254,12 @@
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้ยืม - เงินต้น</t>
+          <t>เงินมัดจำจ่าย</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -3549,7 +4269,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E10" s="17" t="n"/>
@@ -3558,12 +4278,12 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนขายฝาก - เงินต้น</t>
+          <t>ภาษีถูกหัก ณ ที่จ่ายรอเครดิต</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -3573,7 +4293,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E11" s="17" t="n"/>
@@ -3582,12 +4302,12 @@
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนจำนอง - เงินต้น</t>
+          <t>สินทรัพย์หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -3597,7 +4317,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E12" s="17" t="n"/>
@@ -3606,12 +4326,12 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้ยืม - เงินต้น</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -3621,7 +4341,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E13" s="17" t="n"/>
@@ -3630,12 +4350,12 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
+          <t>เงินให้กู้ยืมแบบมีสินทรัพย์ค้ำประกัน - เงินต้น</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -3645,7 +4365,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E14" s="17" t="n"/>
@@ -3654,12 +4374,12 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในหลักทรัพย์</t>
+          <t>เงินลงทุนขายฝาก - เงินต้น</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -3669,7 +4389,7 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E15" s="17" t="n"/>
@@ -3678,12 +4398,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
+          <t>เงินลงทุนจำนอง - เงินต้น</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -3693,7 +4413,7 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E16" s="17" t="n"/>
@@ -3702,12 +4422,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการเช่า</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -3717,7 +4437,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -3726,12 +4446,12 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -3741,7 +4461,7 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E18" s="17" t="n"/>
@@ -3750,22 +4470,22 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการขาย</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E19" s="17" t="n"/>
@@ -3774,22 +4494,22 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
+          <t>เงินลงทุนในหุ้นและหลักทรัพย์</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
@@ -3798,22 +4518,22 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ธนาคาร</t>
+          <t>เงินลงทุนในทองคำ คริปโต และสินทรัพย์ทางเลือก</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E21" s="17" t="n"/>
@@ -3822,22 +4542,22 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมกรรมการ</t>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E22" s="17" t="n"/>
@@ -3846,22 +4566,22 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมอื่น</t>
+          <t>สินทรัพย์ไม่หมุนเวียน</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>สินทรัพย์ไม่หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -3870,17 +4590,17 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -3894,22 +4614,22 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>ทุนตั้งต้น</t>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E25" s="17" t="n"/>
@@ -3918,257 +4638,497 @@
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>กำไรสะสม</t>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E26" s="17" t="n"/>
       <c r="F26" s="18" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="18" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="19" t="n"/>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ธนาคาร</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมกรรมการ</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมอื่น</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียน</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="18" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>ทุนตั้งต้น</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="18" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="18" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนเกินทุนจากการตีราคา (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="18" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>ผลต่างอัตราแลกเปลี่ยนจากการแปลงค่า (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="18" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>รวมสินทรัพย์</t>
         </is>
       </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
-        <v/>
-      </c>
-      <c r="F28" s="19" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="21">
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E23,E24)</f>
+        <v/>
+      </c>
+      <c r="F38" s="19" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>รวมหนี้สิน</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="21">
-        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
-        <v/>
-      </c>
-      <c r="F29" s="19" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="21">
+        <f>SUM(E25,E26,E27,E28,E29,E30,E31,E32)</f>
+        <v/>
+      </c>
+      <c r="F39" s="19" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>รวมส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="21">
-        <f>SUM(E25,E26)</f>
-        <v/>
-      </c>
-      <c r="F30" s="19" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="21">
+        <f>SUM(E33,E34,E35,E36)</f>
+        <v/>
+      </c>
+      <c r="F40" s="19" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n"/>
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="24">
-        <f>E28-E29-E30</f>
-        <v/>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>บัญชี</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>ธนาคาร / ช่องทาง</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="inlineStr">
-        <is>
-          <t>เลขท้าย</t>
-        </is>
-      </c>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>ยอดตั้งต้น</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="28" t="inlineStr">
-        <is>
-          <t>ธนวินท์ - KBANK</t>
-        </is>
-      </c>
-      <c r="C38" s="28" t="inlineStr">
-        <is>
-          <t>กสิกรไทย</t>
-        </is>
-      </c>
-      <c r="D38" s="28" t="inlineStr">
-        <is>
-          <t>5520</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="28" t="inlineStr">
-        <is>
-          <t>ธนวินท์ - BBL</t>
-        </is>
-      </c>
-      <c r="C39" s="28" t="inlineStr">
-        <is>
-          <t>กรุงเทพ</t>
-        </is>
-      </c>
-      <c r="D39" s="28" t="inlineStr">
-        <is>
-          <t>3317</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="29" t="n"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="18" t="n"/>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="22" t="n"/>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="E42" s="24">
+        <f>E38-E39-E40</f>
+        <v/>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>บัญชี</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>ธนาคาร / ช่องทาง</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>เลขท้าย</t>
+        </is>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>ยอดตั้งต้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="28" t="inlineStr">
+        <is>
+          <t>ธนวินท์ - KBANK</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>กสิกรไทย</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="inlineStr">
+        <is>
+          <t>5520</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="28" t="inlineStr">
+        <is>
+          <t>ธนวินท์ - BBL</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="inlineStr">
+        <is>
+          <t>กรุงเทพ</t>
+        </is>
+      </c>
+      <c r="D49" s="28" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="29" t="n"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="2" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="29" t="n"/>
-      <c r="F44" s="2" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="29" t="n"/>
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="18" t="n"/>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="29" t="n"/>
-      <c r="F45" s="2" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="29" t="n"/>
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="20" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="29" t="n"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="29" t="n"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="20" t="inlineStr">
         <is>
           <t>รวมเงินสด</t>
         </is>
       </c>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="19" t="n"/>
-      <c r="E46" s="21">
-        <f>SUM(E38:E45)</f>
-        <v/>
-      </c>
-      <c r="F46" s="30" t="inlineStr">
+      <c r="C56" s="19" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="21">
+        <f>SUM(E48:E55)</f>
+        <v/>
+      </c>
+      <c r="F56" s="30" t="inlineStr">
         <is>
           <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="23" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
         </is>
       </c>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n"/>
-      <c r="E47" s="24">
-        <f>E46-E6</f>
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="22" t="n"/>
+      <c r="E57" s="24">
+        <f>E56-E6</f>
         <v/>
       </c>
     </row>
@@ -4177,7 +5137,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E32">
+  <conditionalFormatting sqref="E42">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -4185,7 +5145,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E47">
+  <conditionalFormatting sqref="E57">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -4203,7 +5163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4351,12 +5311,12 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำจ่าย</t>
+          <t>ลูกหนี้อื่น (รอรับเงิน)</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -4375,12 +5335,12 @@
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้ยืม - เงินต้น</t>
+          <t>เงินมัดจำจ่าย</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -4390,7 +5350,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E10" s="17" t="n"/>
@@ -4399,12 +5359,12 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนขายฝาก - เงินต้น</t>
+          <t>ภาษีถูกหัก ณ ที่จ่ายรอเครดิต</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -4414,7 +5374,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E11" s="17" t="n"/>
@@ -4423,12 +5383,12 @@
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนจำนอง - เงินต้น</t>
+          <t>สินทรัพย์หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -4438,7 +5398,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E12" s="17" t="n"/>
@@ -4447,12 +5407,12 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้ยืม - เงินต้น</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -4462,7 +5422,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E13" s="17" t="n"/>
@@ -4471,12 +5431,12 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
+          <t>เงินให้กู้ยืมแบบมีสินทรัพย์ค้ำประกัน - เงินต้น</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -4486,7 +5446,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E14" s="17" t="n"/>
@@ -4495,12 +5455,12 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในหลักทรัพย์</t>
+          <t>เงินลงทุนขายฝาก - เงินต้น</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -4510,7 +5470,7 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E15" s="17" t="n"/>
@@ -4519,12 +5479,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
+          <t>เงินลงทุนจำนอง - เงินต้น</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -4534,7 +5494,7 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E16" s="17" t="n"/>
@@ -4543,12 +5503,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการเช่า</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -4558,7 +5518,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -4567,12 +5527,12 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -4582,7 +5542,7 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E18" s="17" t="n"/>
@@ -4591,22 +5551,22 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการขาย</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E19" s="17" t="n"/>
@@ -4615,22 +5575,22 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
+          <t>เงินลงทุนในหุ้นและหลักทรัพย์</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
@@ -4639,22 +5599,22 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ธนาคาร</t>
+          <t>เงินลงทุนในทองคำ คริปโต และสินทรัพย์ทางเลือก</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E21" s="17" t="n"/>
@@ -4663,22 +5623,22 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมกรรมการ</t>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E22" s="17" t="n"/>
@@ -4687,22 +5647,22 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมอื่น</t>
+          <t>สินทรัพย์ไม่หมุนเวียน</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>สินทรัพย์ไม่หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -4711,17 +5671,17 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -4735,22 +5695,22 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>ทุนตั้งต้น</t>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E25" s="17" t="n"/>
@@ -4759,239 +5719,479 @@
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>กำไรสะสม</t>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E26" s="17" t="n"/>
       <c r="F26" s="18" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="18" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="19" t="n"/>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ธนาคาร</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมกรรมการ</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมอื่น</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียน</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="18" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>ทุนตั้งต้น</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="18" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="18" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนเกินทุนจากการตีราคา (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="18" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>ผลต่างอัตราแลกเปลี่ยนจากการแปลงค่า (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="18" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>รวมสินทรัพย์</t>
         </is>
       </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
-        <v/>
-      </c>
-      <c r="F28" s="19" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="21">
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E23,E24)</f>
+        <v/>
+      </c>
+      <c r="F38" s="19" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>รวมหนี้สิน</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="21">
-        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
-        <v/>
-      </c>
-      <c r="F29" s="19" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="21">
+        <f>SUM(E25,E26,E27,E28,E29,E30,E31,E32)</f>
+        <v/>
+      </c>
+      <c r="F39" s="19" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>รวมส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="21">
-        <f>SUM(E25,E26)</f>
-        <v/>
-      </c>
-      <c r="F30" s="19" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="21">
+        <f>SUM(E33,E34,E35,E36)</f>
+        <v/>
+      </c>
+      <c r="F40" s="19" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n"/>
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="24">
-        <f>E28-E29-E30</f>
-        <v/>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>บัญชี</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>ธนาคาร / ช่องทาง</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="inlineStr">
-        <is>
-          <t>เลขท้าย</t>
-        </is>
-      </c>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>ยอดตั้งต้น</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="28" t="inlineStr">
-        <is>
-          <t>เบ็ญจพร - BBL</t>
-        </is>
-      </c>
-      <c r="C38" s="28" t="inlineStr">
-        <is>
-          <t>กรุงเทพ</t>
-        </is>
-      </c>
-      <c r="D38" s="28" t="inlineStr">
-        <is>
-          <t>6045</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="18" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="29" t="n"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="18" t="n"/>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="22" t="n"/>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="E42" s="24">
+        <f>E38-E39-E40</f>
+        <v/>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>บัญชี</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>ธนาคาร / ช่องทาง</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>เลขท้าย</t>
+        </is>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>ยอดตั้งต้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="28" t="inlineStr">
+        <is>
+          <t>เบ็ญจพร - BBL</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>กรุงเทพ</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="inlineStr">
+        <is>
+          <t>6045</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="22" t="n"/>
+      <c r="D49" s="22" t="n"/>
+      <c r="E49" s="29" t="n"/>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="2" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="29" t="n"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="29" t="n"/>
-      <c r="F44" s="2" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="20" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="29" t="n"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="29" t="n"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="29" t="n"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>รวมเงินสด</t>
         </is>
       </c>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="21">
-        <f>SUM(E38:E44)</f>
-        <v/>
-      </c>
-      <c r="F45" s="30" t="inlineStr">
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="21">
+        <f>SUM(E48:E54)</f>
+        <v/>
+      </c>
+      <c r="F55" s="30" t="inlineStr">
         <is>
           <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="23" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
         </is>
       </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="24">
-        <f>E45-E6</f>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="24">
+        <f>E55-E6</f>
         <v/>
       </c>
     </row>
@@ -5000,7 +6200,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E32">
+  <conditionalFormatting sqref="E42">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5008,7 +6208,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46">
+  <conditionalFormatting sqref="E56">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -5026,7 +6226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5174,12 +6374,12 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำจ่าย</t>
+          <t>ลูกหนี้อื่น (รอรับเงิน)</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -5198,12 +6398,12 @@
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้ยืม - เงินต้น</t>
+          <t>เงินมัดจำจ่าย</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -5213,7 +6413,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E10" s="17" t="n"/>
@@ -5222,12 +6422,12 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนขายฝาก - เงินต้น</t>
+          <t>ภาษีถูกหัก ณ ที่จ่ายรอเครดิต</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -5237,7 +6437,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E11" s="17" t="n"/>
@@ -5246,12 +6446,12 @@
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนจำนอง - เงินต้น</t>
+          <t>สินทรัพย์หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -5261,7 +6461,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>เงินให้กู้และลงทุนตามสัญญา</t>
+          <t>สินทรัพย์หมุนเวียน</t>
         </is>
       </c>
       <c r="E12" s="17" t="n"/>
@@ -5270,12 +6470,12 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้ยืม - เงินต้น</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -5285,7 +6485,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E13" s="17" t="n"/>
@@ -5294,12 +6494,12 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
+          <t>เงินให้กู้ยืมแบบมีสินทรัพย์ค้ำประกัน - เงินต้น</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -5309,7 +6509,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E14" s="17" t="n"/>
@@ -5318,12 +6518,12 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในหลักทรัพย์</t>
+          <t>เงินลงทุนขายฝาก - เงินต้น</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -5333,7 +6533,7 @@
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E15" s="17" t="n"/>
@@ -5342,12 +6542,12 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในทองคำและสินทรัพย์ทางเลือก</t>
+          <t>เงินลงทุนจำนอง - เงินต้น</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -5357,7 +6557,7 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>เงินให้กู้และลงทุนตามสัญญา</t>
         </is>
       </c>
       <c r="E16" s="17" t="n"/>
@@ -5366,12 +6566,12 @@
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุนในบริษัทในเครือ</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการเช่า</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
@@ -5381,7 +6581,7 @@
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>เงินลงทุน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -5390,12 +6590,12 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ค่ารีโนเวท (บันทึกเป็นทุน)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -5405,7 +6605,7 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E18" s="17" t="n"/>
@@ -5414,22 +6614,22 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน เพื่อการขาย</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>อสังหาริมทรัพย์เพื่อการลงทุน</t>
         </is>
       </c>
       <c r="E19" s="17" t="n"/>
@@ -5438,22 +6638,22 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>เงินมัดจำรับจากผู้เช่า</t>
+          <t>เงินลงทุนในหุ้นและหลักทรัพย์</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>หนี้สินหมุนเวียน</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E20" s="17" t="n"/>
@@ -5462,22 +6662,22 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ธนาคาร</t>
+          <t>เงินลงทุนในทองคำ คริปโต และสินทรัพย์ทางเลือก</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E21" s="17" t="n"/>
@@ -5486,22 +6686,22 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมกรรมการ</t>
+          <t>เงินลงทุนในบริษัทในเครือ</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>เงินลงทุน</t>
         </is>
       </c>
       <c r="E22" s="17" t="n"/>
@@ -5510,22 +6710,22 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้ยืมอื่น</t>
+          <t>สินทรัพย์ไม่หมุนเวียน</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>เงินกู้</t>
+          <t>สินทรัพย์ไม่หมุนเวียนอื่น</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -5534,17 +6734,17 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+          <t>ลูกหนี้ระหว่างกัน (ในกองกลาง)</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>หนี้สิน</t>
+          <t>สินทรัพย์</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
@@ -5558,22 +6758,22 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>ทุนตั้งต้น</t>
+          <t>เจ้าหนี้การค้า-เจ้าหนี้อื่น</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E25" s="17" t="n"/>
@@ -5582,239 +6782,479 @@
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>กำไรสะสม</t>
+          <t>เงินมัดจำรับจากผู้เช่า</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สิน</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>ส่วนของเจ้าของ</t>
+          <t>หนี้สินหมุนเวียน</t>
         </is>
       </c>
       <c r="E26" s="17" t="n"/>
       <c r="F26" s="18" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินหมุนเวียน</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="18" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="19" t="n"/>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>2410</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ธนาคาร</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมกรรมการ</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้ยืมอื่น</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>เงินกู้</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียน</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สินไม่หมุนเวียนอื่น</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="18" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>เจ้าหนี้ระหว่างกัน (ในกองกลาง)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>หนี้สิน</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>รายการระหว่างกัน (ตัดออกในงบรวม)</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>ทุนตั้งต้น</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="18" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>กำไรสะสม</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="18" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนเกินทุนจากการตีราคา (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="18" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>ผลต่างอัตราแลกเปลี่ยนจากการแปลงค่า (ยังไม่เกิดขึ้นจริง)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>ส่วนของเจ้าของ</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="18" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>รวมสินทรัพย์</t>
         </is>
       </c>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="21">
-        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18)</f>
-        <v/>
-      </c>
-      <c r="F28" s="19" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="21">
+        <f>SUM(E6,E7,E8,E9,E10,E11,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E23,E24)</f>
+        <v/>
+      </c>
+      <c r="F38" s="19" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>รวมหนี้สิน</t>
         </is>
       </c>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="21">
-        <f>SUM(E19,E20,E21,E22,E23,E24)</f>
-        <v/>
-      </c>
-      <c r="F29" s="19" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="21">
+        <f>SUM(E25,E26,E27,E28,E29,E30,E31,E32)</f>
+        <v/>
+      </c>
+      <c r="F39" s="19" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>รวมส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="21">
-        <f>SUM(E25,E26)</f>
-        <v/>
-      </c>
-      <c r="F30" s="19" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="22" t="n"/>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="21">
+        <f>SUM(E33,E34,E35,E36)</f>
+        <v/>
+      </c>
+      <c r="F40" s="19" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n"/>
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: สินทรัพย์ − หนี้สิน − ส่วนของเจ้าของ</t>
         </is>
       </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="24">
-        <f>E28-E29-E30</f>
-        <v/>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>บัญชี</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>ธนาคาร / ช่องทาง</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="inlineStr">
-        <is>
-          <t>เลขท้าย</t>
-        </is>
-      </c>
-      <c r="E37" s="27" t="inlineStr">
-        <is>
-          <t>ยอดตั้งต้น</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="28" t="inlineStr">
-        <is>
-          <t>สุดจิตต์ - BAY</t>
-        </is>
-      </c>
-      <c r="C38" s="28" t="inlineStr">
-        <is>
-          <t>กรุงศรีอยุธยา</t>
-        </is>
-      </c>
-      <c r="D38" s="28" t="inlineStr">
-        <is>
-          <t>7702</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="18" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="29" t="n"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="29" t="n"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="18" t="n"/>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="22" t="n"/>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="E42" s="24">
+        <f>E38-E39-E40</f>
+        <v/>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>ต้องเป็น 0 — ถ้าไม่ใช่ ใส่ผลต่างที่ 3300 กำไรสะสม แล้วเขียนหมายเหตุไว้</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>แยกยอดเงินสดตามบัญชี (ต้องรวมได้เท่าบรรทัด 1100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>บัญชีที่ระบบมีอยู่แล้วเติมให้ · บัญชีใหม่กรอกในแถวว่างด้านล่าง · ทุกบาทของบรรทัด 1100 ต้องมีบัญชีรองรับ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>บัญชี</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>ธนาคาร / ช่องทาง</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>เลขท้าย</t>
+        </is>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>ยอดตั้งต้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="28" t="inlineStr">
+        <is>
+          <t>สุดจิตต์ - BAY</t>
+        </is>
+      </c>
+      <c r="C48" s="28" t="inlineStr">
+        <is>
+          <t>กรุงศรีอยุธยา</t>
+        </is>
+      </c>
+      <c r="D48" s="28" t="inlineStr">
+        <is>
+          <t>7702</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="22" t="n"/>
+      <c r="D49" s="22" t="n"/>
+      <c r="E49" s="29" t="n"/>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="29" t="n"/>
-      <c r="F43" s="2" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="29" t="n"/>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="29" t="n"/>
-      <c r="F44" s="2" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="20" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="29" t="n"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="29" t="n"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="29" t="n"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>← บัญชีใหม่ที่ยังไม่มีในระบบ กรอกชื่อ+ธนาคาร+ยอด</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>รวมเงินสด</t>
         </is>
       </c>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="21">
-        <f>SUM(E38:E44)</f>
-        <v/>
-      </c>
-      <c r="F45" s="30" t="inlineStr">
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="21">
+        <f>SUM(E48:E54)</f>
+        <v/>
+      </c>
+      <c r="F55" s="30" t="inlineStr">
         <is>
           <t>ต้องเท่ากับบรรทัด 1100 (แถว 6)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="23" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="23" t="inlineStr">
         <is>
           <t>ตรวจ: ผลต่างกับบรรทัด 1100</t>
         </is>
       </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="24">
-        <f>E45-E6</f>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="24">
+        <f>E55-E6</f>
         <v/>
       </c>
     </row>
@@ -5823,7 +7263,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E32">
+  <conditionalFormatting sqref="E42">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5831,7 +7271,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46">
+  <conditionalFormatting sqref="E56">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -5935,27 +7375,27 @@
         </is>
       </c>
       <c r="B6" s="17">
-        <f>'BS-SRI Corporation'!E28</f>
+        <f>'BS-SRI Corporation'!E38</f>
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>'BS-สุธี'!E28</f>
+        <f>'BS-สุธี'!E38</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>'BS-ธนากร'!E28</f>
+        <f>'BS-ธนากร'!E38</f>
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>'BS-ธนวินท์'!E28</f>
+        <f>'BS-ธนวินท์'!E38</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>'BS-เบ็ญจพร'!E28</f>
+        <f>'BS-เบ็ญจพร'!E38</f>
         <v/>
       </c>
       <c r="G6" s="17">
-        <f>'BS-สุดจิตต์'!E28</f>
+        <f>'BS-สุดจิตต์'!E38</f>
         <v/>
       </c>
       <c r="H6" s="24">
@@ -5970,27 +7410,27 @@
         </is>
       </c>
       <c r="B7" s="17">
-        <f>'BS-SRI Corporation'!E29</f>
+        <f>'BS-SRI Corporation'!E39</f>
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>'BS-สุธี'!E29</f>
+        <f>'BS-สุธี'!E39</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>'BS-ธนากร'!E29</f>
+        <f>'BS-ธนากร'!E39</f>
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>'BS-ธนวินท์'!E29</f>
+        <f>'BS-ธนวินท์'!E39</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>'BS-เบ็ญจพร'!E29</f>
+        <f>'BS-เบ็ญจพร'!E39</f>
         <v/>
       </c>
       <c r="G7" s="17">
-        <f>'BS-สุดจิตต์'!E29</f>
+        <f>'BS-สุดจิตต์'!E39</f>
         <v/>
       </c>
       <c r="H7" s="24">
@@ -6005,27 +7445,27 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>'BS-SRI Corporation'!E30</f>
+        <f>'BS-SRI Corporation'!E40</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>'BS-สุธี'!E30</f>
+        <f>'BS-สุธี'!E40</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>'BS-ธนากร'!E30</f>
+        <f>'BS-ธนากร'!E40</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>'BS-ธนวินท์'!E30</f>
+        <f>'BS-ธนวินท์'!E40</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>'BS-เบ็ญจพร'!E30</f>
+        <f>'BS-เบ็ญจพร'!E40</f>
         <v/>
       </c>
       <c r="G8" s="17">
-        <f>'BS-สุดจิตต์'!E30</f>
+        <f>'BS-สุดจิตต์'!E40</f>
         <v/>
       </c>
       <c r="H8" s="24">
@@ -6040,27 +7480,27 @@
         </is>
       </c>
       <c r="B10" s="24">
-        <f>'BS-SRI Corporation'!E32</f>
+        <f>'BS-SRI Corporation'!E42</f>
         <v/>
       </c>
       <c r="C10" s="24">
-        <f>'BS-สุธี'!E32</f>
+        <f>'BS-สุธี'!E42</f>
         <v/>
       </c>
       <c r="D10" s="24">
-        <f>'BS-ธนากร'!E32</f>
+        <f>'BS-ธนากร'!E42</f>
         <v/>
       </c>
       <c r="E10" s="24">
-        <f>'BS-ธนวินท์'!E32</f>
+        <f>'BS-ธนวินท์'!E42</f>
         <v/>
       </c>
       <c r="F10" s="24">
-        <f>'BS-เบ็ญจพร'!E32</f>
+        <f>'BS-เบ็ญจพร'!E42</f>
         <v/>
       </c>
       <c r="G10" s="24">
-        <f>'BS-สุดจิตต์'!E32</f>
+        <f>'BS-สุดจิตต์'!E42</f>
         <v/>
       </c>
     </row>
@@ -6078,27 +7518,27 @@
         </is>
       </c>
       <c r="B13" s="17">
-        <f>'BS-SRI Corporation'!E18</f>
+        <f>'BS-SRI Corporation'!E24</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>'BS-สุธี'!E18</f>
+        <f>'BS-สุธี'!E24</f>
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>'BS-ธนากร'!E18</f>
+        <f>'BS-ธนากร'!E24</f>
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>'BS-ธนวินท์'!E18</f>
+        <f>'BS-ธนวินท์'!E24</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>'BS-เบ็ญจพร'!E18</f>
+        <f>'BS-เบ็ญจพร'!E24</f>
         <v/>
       </c>
       <c r="G13" s="17">
-        <f>'BS-สุดจิตต์'!E18</f>
+        <f>'BS-สุดจิตต์'!E24</f>
         <v/>
       </c>
       <c r="H13" s="24">
@@ -6113,27 +7553,27 @@
         </is>
       </c>
       <c r="B14" s="17">
-        <f>'BS-SRI Corporation'!E24</f>
+        <f>'BS-SRI Corporation'!E32</f>
         <v/>
       </c>
       <c r="C14" s="17">
-        <f>'BS-สุธี'!E24</f>
+        <f>'BS-สุธี'!E32</f>
         <v/>
       </c>
       <c r="D14" s="17">
-        <f>'BS-ธนากร'!E24</f>
+        <f>'BS-ธนากร'!E32</f>
         <v/>
       </c>
       <c r="E14" s="17">
-        <f>'BS-ธนวินท์'!E24</f>
+        <f>'BS-ธนวินท์'!E32</f>
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>'BS-เบ็ญจพร'!E24</f>
+        <f>'BS-เบ็ญจพร'!E32</f>
         <v/>
       </c>
       <c r="G14" s="17">
-        <f>'BS-สุดจิตต์'!E24</f>
+        <f>'BS-สุดจิตต์'!E32</f>
         <v/>
       </c>
       <c r="H14" s="24">
